--- a/Simulador_PMM.xlsx
+++ b/Simulador_PMM.xlsx
@@ -12,14 +12,20 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="75">
   <si>
     <t>SIMULADOR PÓLIZA MULTIPRODUCTO MULTIEMPRESA (PMM)</t>
   </si>
   <si>
+    <t>Contrato de Afianzamiento — Póliza Paraguas</t>
+  </si>
+  <si>
     <t>LÍMITE GLOBAL PMM:</t>
   </si>
   <si>
+    <t>DISPONIBLE GLOBAL:</t>
+  </si>
+  <si>
     <t>MATRIZ DE DISPOSICIONES POR EMPRESA Y PRODUCTO</t>
   </si>
   <si>
@@ -119,22 +125,58 @@
     <t>Margen Global</t>
   </si>
   <si>
-    <t>INSTRUCCIONES DE USO - SIMULADOR PMM</t>
-  </si>
-  <si>
-    <t>1. LÍMITE GLOBAL</t>
-  </si>
-  <si>
-    <t>Celda C3 en hoja "Simulador PMM"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   Modifique el valor del límite global de la póliza paraguas.</t>
-  </si>
-  <si>
-    <t>2. SUBLÍMITES POR PRODUCTO</t>
-  </si>
-  <si>
-    <t>Columna B, filas 7-11</t>
+    <t>LEYENDA</t>
+  </si>
+  <si>
+    <t>🟡 Amarillo claro</t>
+  </si>
+  <si>
+    <t>Celda editable — disposiciones por empresa</t>
+  </si>
+  <si>
+    <t>🔵 Azul claro</t>
+  </si>
+  <si>
+    <t>Celda editable — sublímite de producto / límite global</t>
+  </si>
+  <si>
+    <t>🟢 Verde claro</t>
+  </si>
+  <si>
+    <t>Disponible (calculado automáticamente)</t>
+  </si>
+  <si>
+    <t>🔴 Rojo / "ERROR"</t>
+  </si>
+  <si>
+    <t>Límite excedido — sublímite o global superado</t>
+  </si>
+  <si>
+    <t>⚡ Ámbar</t>
+  </si>
+  <si>
+    <t>Utilización &gt; 80% (alerta preventiva)</t>
+  </si>
+  <si>
+    <t>✓ OK</t>
+  </si>
+  <si>
+    <t>Dentro de parámetros</t>
+  </si>
+  <si>
+    <t>INSTRUCCIONES DE USO — SIMULADOR PMM</t>
+  </si>
+  <si>
+    <t>1. LÍMITE GLOBAL (celda C3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Modifique el límite global de la póliza paraguas.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   El disponible global se muestra en G3:H3 y se actualiza automáticamente.</t>
+  </si>
+  <si>
+    <t>2. SUBLÍMITES POR PRODUCTO (columna B, filas 7-11)</t>
   </si>
   <si>
     <t xml:space="preserve">   Modifique los sublímites de cada tipo de producto.</t>
@@ -143,58 +185,58 @@
     <t xml:space="preserve">   Los sublímites pueden superar el límite global (son techos por producto).</t>
   </si>
   <si>
-    <t>3. DISPOSICIONES POR EMPRESA</t>
-  </si>
-  <si>
-    <t>Columnas C-F, filas 7-11 (celdas amarillas)</t>
+    <t>3. DISPOSICIONES POR EMPRESA (celdas amarillas, C7:F11)</t>
   </si>
   <si>
     <t xml:space="preserve">   Introduzca los importes dispuestos por cada empresa en cada producto.</t>
   </si>
   <si>
-    <t xml:space="preserve">   Las celdas amarillas son editables. No se permiten valores negativos.</t>
-  </si>
-  <si>
-    <t>4. INDICADORES AUTOMÁTICOS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   - Total Dispuesto: suma de disposiciones por producto y empresa.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   - Disponible: MIN(sublímite - dispuesto, límite global - total global).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   - % Utilización: porcentaje del sublímite consumido.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   - El disponible nunca permite superar el límite global.</t>
-  </si>
-  <si>
-    <t>5. ALERTAS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   - Rojo: sublímite o límite global excedido / disponible negativo.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   - Ámbar: utilización &gt; 80%.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   - ⚠ EXCEDIDO: se ha superado un límite.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   - ✓ OK: dentro de parámetros.</t>
-  </si>
-  <si>
-    <t>6. REGLA CLAVE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   El límite global NO puede superarse en ningún momento.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   El disponible por producto se ajusta automáticamente para</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   respetar tanto el sublímite del producto como el límite global.</t>
+    <t xml:space="preserve">   No se permiten valores negativos.</t>
+  </si>
+  <si>
+    <t>4. SISTEMA DE ALERTAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   • "ERROR" (rojo): el total dispuesto supera el sublímite del producto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">     O el total global supera el límite PMM.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   • Disponible = 0 (rojo): no queda margen disponible.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   • ⚡ ALTO (ámbar): utilización superior al 80%.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   • ✓ OK (verde): dentro de parámetros.</t>
+  </si>
+  <si>
+    <t>5. REGLA FUNDAMENTAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   El límite global NO puede superarse. El disponible por producto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   se ajusta automáticamente respetando AMBOS techos (sublímite y global).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Los valores nunca serán negativos: mínimo 0 o texto ERROR.</t>
+  </si>
+  <si>
+    <t>6. CELDAS EDITABLES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   • C3: Límite global PMM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   • B7:B11: Sublímites por producto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   • C7:F11: Disposiciones por empresa y producto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Todas las demás celdas son de cálculo automático.</t>
   </si>
 </sst>
 </file>
@@ -202,10 +244,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="#,##0€"/>
+    <numFmt numFmtId="164" formatCode="#,##0 €"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -217,6 +259,18 @@
       <b/>
       <color rgb="FFFFFF"/>
       <sz val="14"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <i/>
+      <color rgb="B2DFDB"/>
+      <sz val="10"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <i/>
+      <color rgb="607D8B"/>
+      <sz val="9"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -280,6 +334,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="C8E6C9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="004D40"/>
       </patternFill>
     </fill>
@@ -300,21 +359,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="C8E6C9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFFF"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00838F"/>
+      </left>
+      <right style="medium">
+        <color rgb="00838F"/>
+      </right>
+      <top style="medium">
+        <color rgb="00838F"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="00838F"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -336,111 +405,125 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="9" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="8" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="8" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="165" fontId="8" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="13">
     <dxf>
       <font>
         <b/>
-        <color rgb="F44336"/>
+        <color rgb="C62828"/>
+        <sz val="10"/>
+        <name val="Calibri"/>
       </font>
       <fill>
         <patternFill patternType="solid">
@@ -451,7 +534,9 @@
     <dxf>
       <font>
         <b/>
-        <color rgb="F44336"/>
+        <color rgb="C62828"/>
+        <sz val="10"/>
+        <name val="Calibri"/>
       </font>
       <fill>
         <patternFill patternType="solid">
@@ -462,7 +547,124 @@
     <dxf>
       <font>
         <b/>
-        <color rgb="F44336"/>
+        <color rgb="C62828"/>
+        <sz val="10"/>
+        <name val="Calibri"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFCDD2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="E65100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF3E0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="C62828"/>
+        <sz val="10"/>
+        <name val="Calibri"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFCDD2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="C62828"/>
+        <sz val="10"/>
+        <name val="Calibri"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFCDD2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="C62828"/>
+        <sz val="10"/>
+        <name val="Calibri"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFCDD2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="C62828"/>
+        <sz val="10"/>
+        <name val="Calibri"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFCDD2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="C62828"/>
+        <sz val="10"/>
+        <name val="Calibri"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFCDD2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="C62828"/>
+        <sz val="10"/>
+        <name val="Calibri"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFCDD2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="C62828"/>
+        <sz val="10"/>
+        <name val="Calibri"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFCDD2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="C62828"/>
+        <sz val="10"/>
+        <name val="Calibri"/>
       </font>
       <fill>
         <patternFill patternType="solid">
@@ -820,7 +1022,7 @@
     <tabColor rgb="00838F"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I34"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
@@ -843,501 +1045,609 @@
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
     </row>
-    <row r="3" ht="30" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+    <row r="2" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="2"/>
-      <c r="C3" s="3">
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="G2" s="3">
+        <f>TEXT(TODAY(),""Fecha simulación: "DD/MM/YYYY")</f>
+      </c>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+    </row>
+    <row r="3" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="4"/>
+      <c r="C3" s="5">
         <v>8000000</v>
       </c>
+      <c r="E3" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F3" s="4"/>
+      <c r="G3" s="6">
+        <f>MAX(0,$C$3-SUM($C$7:$F$11))</f>
+      </c>
+      <c r="H3" s="6"/>
     </row>
     <row r="5" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B5" s="4"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="4"/>
-      <c r="I5" s="4"/>
+      <c r="A5" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="7"/>
+      <c r="C5" s="7"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="7"/>
+      <c r="H5" s="7"/>
+      <c r="I5" s="7"/>
     </row>
     <row r="6" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C6" s="5" t="s">
+      <c r="A6" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="B6" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="C6" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="D6" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="G6" s="5" t="s">
+      <c r="E6" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="H6" s="5" t="s">
+      <c r="F6" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="I6" s="5" t="s">
+      <c r="G6" s="8" t="s">
         <v>11</v>
       </c>
+      <c r="H6" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="I6" s="8" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="6" t="s">
+      <c r="A7" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="10">
+        <v>2000000</v>
+      </c>
+      <c r="C7" s="11">
+        <v>500000</v>
+      </c>
+      <c r="D7" s="11">
+        <v>300000</v>
+      </c>
+      <c r="E7" s="11">
+        <v>200000</v>
+      </c>
+      <c r="F7" s="11">
+        <v>400000</v>
+      </c>
+      <c r="G7" s="12">
+        <f>IF(OR(SUM(C7:F7)&gt;B7,SUM($C$7:$F$11)&gt;$C$3),"ERROR",SUM(C7:F7))</f>
+      </c>
+      <c r="H7" s="13">
+        <f>IF(NOT(ISNUMBER(G7)),0,MAX(0,MIN(B7-SUM(C7:F7),MAX(0,$C$3-SUM($C$7:$F$11)))))</f>
+      </c>
+      <c r="I7" s="14">
+        <f>IF(NOT(ISNUMBER(G7)),"—",IF(B7=0,0,SUM(C7:F7)/B7))</f>
+      </c>
+    </row>
+    <row r="8" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="10">
+        <v>8000000</v>
+      </c>
+      <c r="C8" s="11">
+        <v>1000000</v>
+      </c>
+      <c r="D8" s="11">
+        <v>500000</v>
+      </c>
+      <c r="E8" s="11">
+        <v>800000</v>
+      </c>
+      <c r="F8" s="11">
+        <v>700000</v>
+      </c>
+      <c r="G8" s="12">
+        <f>IF(OR(SUM(C8:F8)&gt;B8,SUM($C$7:$F$11)&gt;$C$3),"ERROR",SUM(C8:F8))</f>
+      </c>
+      <c r="H8" s="13">
+        <f>IF(NOT(ISNUMBER(G8)),0,MAX(0,MIN(B8-SUM(C8:F8),MAX(0,$C$3-SUM($C$7:$F$11)))))</f>
+      </c>
+      <c r="I8" s="16">
+        <f>IF(NOT(ISNUMBER(G8)),"—",IF(B8=0,0,SUM(C8:F8)/B8))</f>
+      </c>
+    </row>
+    <row r="9" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="10">
+        <v>8000000</v>
+      </c>
+      <c r="C9" s="11">
+        <v>300000</v>
+      </c>
+      <c r="D9" s="11">
+        <v>200000</v>
+      </c>
+      <c r="E9" s="11">
+        <v>400000</v>
+      </c>
+      <c r="F9" s="11">
+        <v>100000</v>
+      </c>
+      <c r="G9" s="12">
+        <f>IF(OR(SUM(C9:F9)&gt;B9,SUM($C$7:$F$11)&gt;$C$3),"ERROR",SUM(C9:F9))</f>
+      </c>
+      <c r="H9" s="13">
+        <f>IF(NOT(ISNUMBER(G9)),0,MAX(0,MIN(B9-SUM(C9:F9),MAX(0,$C$3-SUM($C$7:$F$11)))))</f>
+      </c>
+      <c r="I9" s="14">
+        <f>IF(NOT(ISNUMBER(G9)),"—",IF(B9=0,0,SUM(C9:F9)/B9))</f>
+      </c>
+    </row>
+    <row r="10" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="10">
+        <v>8000000</v>
+      </c>
+      <c r="C10" s="11">
+        <v>0</v>
+      </c>
+      <c r="D10" s="11">
+        <v>100000</v>
+      </c>
+      <c r="E10" s="11">
+        <v>200000</v>
+      </c>
+      <c r="F10" s="11">
+        <v>0</v>
+      </c>
+      <c r="G10" s="12">
+        <f>IF(OR(SUM(C10:F10)&gt;B10,SUM($C$7:$F$11)&gt;$C$3),"ERROR",SUM(C10:F10))</f>
+      </c>
+      <c r="H10" s="13">
+        <f>IF(NOT(ISNUMBER(G10)),0,MAX(0,MIN(B10-SUM(C10:F10),MAX(0,$C$3-SUM($C$7:$F$11)))))</f>
+      </c>
+      <c r="I10" s="16">
+        <f>IF(NOT(ISNUMBER(G10)),"—",IF(B10=0,0,SUM(C10:F10)/B10))</f>
+      </c>
+    </row>
+    <row r="11" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="10">
+        <v>4000000</v>
+      </c>
+      <c r="C11" s="11">
+        <v>500000</v>
+      </c>
+      <c r="D11" s="11">
+        <v>300000</v>
+      </c>
+      <c r="E11" s="11">
+        <v>400000</v>
+      </c>
+      <c r="F11" s="11">
+        <v>300000</v>
+      </c>
+      <c r="G11" s="12">
+        <f>IF(OR(SUM(C11:F11)&gt;B11,SUM($C$7:$F$11)&gt;$C$3),"ERROR",SUM(C11:F11))</f>
+      </c>
+      <c r="H11" s="13">
+        <f>IF(NOT(ISNUMBER(G11)),0,MAX(0,MIN(B11-SUM(C11:F11),MAX(0,$C$3-SUM($C$7:$F$11)))))</f>
+      </c>
+      <c r="I11" s="14">
+        <f>IF(NOT(ISNUMBER(G11)),"—",IF(B11=0,0,SUM(C11:F11)/B11))</f>
+      </c>
+    </row>
+    <row r="12" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="18">
+        <f>SUM(B7:B11)</f>
+      </c>
+      <c r="C12" s="18">
+        <f>SUM(C7:C11)</f>
+      </c>
+      <c r="D12" s="18">
+        <f>SUM(D7:D11)</f>
+      </c>
+      <c r="E12" s="18">
+        <f>SUM(E7:E11)</f>
+      </c>
+      <c r="F12" s="18">
+        <f>SUM(F7:F11)</f>
+      </c>
+      <c r="G12" s="18">
+        <f>IF(SUM($C$7:$F$11)&gt;$C$3,"ERROR",SUM($C$7:$F$11))</f>
+      </c>
+      <c r="H12" s="18">
+        <f>IF(NOT(ISNUMBER(G12)),0,MAX(0,$C$3-SUM($C$7:$F$11)))</f>
+      </c>
+      <c r="I12" s="19">
+        <f>IF(NOT(ISNUMBER(G12)),"—",IF($C$3=0,0,SUM($C$7:$F$11)/$C$3))</f>
+      </c>
+    </row>
+    <row r="14" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B14" s="7"/>
+      <c r="C14" s="7"/>
+      <c r="D14" s="7"/>
+      <c r="E14" s="7"/>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="16" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="B16" s="20">
+        <f>$C$3</f>
+      </c>
+      <c r="C16" s="14">
+        <v>1</v>
+      </c>
+      <c r="D16" s="21" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="17" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="B17" s="23">
+        <f>IF(SUM($C$7:$F$11)&gt;$C$3,"ERROR",SUM($C$7:$F$11))</f>
+      </c>
+      <c r="C17" s="24">
+        <f>IF(NOT(ISNUMBER(B17)),"—",IF($C$3=0,0,SUM($C$7:$F$11)/$C$3))</f>
+      </c>
+      <c r="D17" s="25">
+        <f>IF(NOT(ISNUMBER(B17)),"⚠ EXCEDIDO","✓ OK")</f>
+      </c>
+    </row>
+    <row r="18" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="B18" s="13">
+        <f>IF(NOT(ISNUMBER(B17)),0,MAX(0,$C$3-SUM($C$7:$F$11)))</f>
+      </c>
+      <c r="C18" s="27">
+        <f>IF($C$3=0,0,B18/$C$3)</f>
+      </c>
+      <c r="D18" s="28">
+        <f>IF(B18=0,"⚠ SIN DISPONIBLE","✓ DISPONIBLE")</f>
+      </c>
+    </row>
+    <row r="20" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A20" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B20" s="7"/>
+      <c r="C20" s="7"/>
+      <c r="D20" s="7"/>
+      <c r="E20" s="7"/>
+      <c r="F20" s="7"/>
+      <c r="G20" s="7"/>
+      <c r="H20" s="7"/>
+      <c r="I20" s="7"/>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A21" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="D21" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="7">
-        <v>2000000</v>
-      </c>
-      <c r="C7" s="8">
-        <v>500000</v>
-      </c>
-      <c r="D7" s="8">
-        <v>300000</v>
-      </c>
-      <c r="E7" s="8">
-        <v>200000</v>
-      </c>
-      <c r="F7" s="8">
-        <v>400000</v>
-      </c>
-      <c r="G7" s="9">
+      <c r="E21" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="F21" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="G21" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="H21" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="I21" s="8" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="22" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A22" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B22" s="29">
+        <f>B7</f>
+      </c>
+      <c r="C22" s="29">
         <f>SUM(C7:F7)</f>
       </c>
-      <c r="H7" s="10">
-        <f>MIN(B7-G7, MAX(0, $C$3-G$12))</f>
-      </c>
-      <c r="I7" s="11">
-        <f>IF(B7=0,0,G7/B7)</f>
-      </c>
-    </row>
-    <row r="8" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="B8" s="7">
-        <v>8000000</v>
-      </c>
-      <c r="C8" s="8">
-        <v>1000000</v>
-      </c>
-      <c r="D8" s="8">
-        <v>500000</v>
-      </c>
-      <c r="E8" s="8">
-        <v>800000</v>
-      </c>
-      <c r="F8" s="8">
-        <v>700000</v>
-      </c>
-      <c r="G8" s="9">
+      <c r="D22" s="13">
+        <f>MAX(0,H7)</f>
+      </c>
+      <c r="E22" s="30">
+        <f>IF(B22=0,0,C22/B22)</f>
+      </c>
+      <c r="F22" s="30">
+        <f>IF($C$3=0,0,C22/$C$3)</f>
+      </c>
+      <c r="G22" s="21">
+        <f>IF(C22&gt;B22,"⚠ EXCEDIDO",IF(B22=0,"—",IF(C22/B22&gt;0.8,"⚡ ALTO","✓ OK")))</f>
+      </c>
+      <c r="H22" s="21">
+        <f>IF(SUM($C$7:$F$11)&gt;$C$3,"⚠ EXCEDIDO","✓ OK")</f>
+      </c>
+      <c r="I22" s="29">
+        <f>MAX(0,$C$3-SUM($C$7:$F$11))</f>
+      </c>
+    </row>
+    <row r="23" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A23" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="B23" s="31">
+        <f>B8</f>
+      </c>
+      <c r="C23" s="31">
         <f>SUM(C8:F8)</f>
       </c>
-      <c r="H8" s="10">
-        <f>MIN(B8-G8, MAX(0, $C$3-G$12))</f>
-      </c>
-      <c r="I8" s="13">
-        <f>IF(B8=0,0,G8/B8)</f>
-      </c>
-    </row>
-    <row r="9" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" s="7">
-        <v>8000000</v>
-      </c>
-      <c r="C9" s="8">
-        <v>300000</v>
-      </c>
-      <c r="D9" s="8">
-        <v>200000</v>
-      </c>
-      <c r="E9" s="8">
-        <v>400000</v>
-      </c>
-      <c r="F9" s="8">
-        <v>100000</v>
-      </c>
-      <c r="G9" s="9">
+      <c r="D23" s="13">
+        <f>MAX(0,H8)</f>
+      </c>
+      <c r="E23" s="32">
+        <f>IF(B23=0,0,C23/B23)</f>
+      </c>
+      <c r="F23" s="32">
+        <f>IF($C$3=0,0,C23/$C$3)</f>
+      </c>
+      <c r="G23" s="33">
+        <f>IF(C23&gt;B23,"⚠ EXCEDIDO",IF(B23=0,"—",IF(C23/B23&gt;0.8,"⚡ ALTO","✓ OK")))</f>
+      </c>
+      <c r="H23" s="33">
+        <f>IF(SUM($C$7:$F$11)&gt;$C$3,"⚠ EXCEDIDO","✓ OK")</f>
+      </c>
+      <c r="I23" s="31">
+        <f>MAX(0,$C$3-SUM($C$7:$F$11))</f>
+      </c>
+    </row>
+    <row r="24" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A24" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B24" s="29">
+        <f>B9</f>
+      </c>
+      <c r="C24" s="29">
         <f>SUM(C9:F9)</f>
       </c>
-      <c r="H9" s="10">
-        <f>MIN(B9-G9, MAX(0, $C$3-G$12))</f>
-      </c>
-      <c r="I9" s="11">
-        <f>IF(B9=0,0,G9/B9)</f>
-      </c>
-    </row>
-    <row r="10" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="B10" s="7">
-        <v>8000000</v>
-      </c>
-      <c r="C10" s="8">
-        <v>0</v>
-      </c>
-      <c r="D10" s="8">
-        <v>100000</v>
-      </c>
-      <c r="E10" s="8">
-        <v>200000</v>
-      </c>
-      <c r="F10" s="8">
-        <v>0</v>
-      </c>
-      <c r="G10" s="9">
+      <c r="D24" s="13">
+        <f>MAX(0,H9)</f>
+      </c>
+      <c r="E24" s="30">
+        <f>IF(B24=0,0,C24/B24)</f>
+      </c>
+      <c r="F24" s="30">
+        <f>IF($C$3=0,0,C24/$C$3)</f>
+      </c>
+      <c r="G24" s="21">
+        <f>IF(C24&gt;B24,"⚠ EXCEDIDO",IF(B24=0,"—",IF(C24/B24&gt;0.8,"⚡ ALTO","✓ OK")))</f>
+      </c>
+      <c r="H24" s="21">
+        <f>IF(SUM($C$7:$F$11)&gt;$C$3,"⚠ EXCEDIDO","✓ OK")</f>
+      </c>
+      <c r="I24" s="29">
+        <f>MAX(0,$C$3-SUM($C$7:$F$11))</f>
+      </c>
+    </row>
+    <row r="25" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A25" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="B25" s="31">
+        <f>B10</f>
+      </c>
+      <c r="C25" s="31">
         <f>SUM(C10:F10)</f>
       </c>
-      <c r="H10" s="10">
-        <f>MIN(B10-G10, MAX(0, $C$3-G$12))</f>
-      </c>
-      <c r="I10" s="13">
-        <f>IF(B10=0,0,G10/B10)</f>
-      </c>
-    </row>
-    <row r="11" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="B11" s="7">
-        <v>4000000</v>
-      </c>
-      <c r="C11" s="8">
-        <v>500000</v>
-      </c>
-      <c r="D11" s="8">
-        <v>300000</v>
-      </c>
-      <c r="E11" s="8">
-        <v>400000</v>
-      </c>
-      <c r="F11" s="8">
-        <v>300000</v>
-      </c>
-      <c r="G11" s="9">
+      <c r="D25" s="13">
+        <f>MAX(0,H10)</f>
+      </c>
+      <c r="E25" s="32">
+        <f>IF(B25=0,0,C25/B25)</f>
+      </c>
+      <c r="F25" s="32">
+        <f>IF($C$3=0,0,C25/$C$3)</f>
+      </c>
+      <c r="G25" s="33">
+        <f>IF(C25&gt;B25,"⚠ EXCEDIDO",IF(B25=0,"—",IF(C25/B25&gt;0.8,"⚡ ALTO","✓ OK")))</f>
+      </c>
+      <c r="H25" s="33">
+        <f>IF(SUM($C$7:$F$11)&gt;$C$3,"⚠ EXCEDIDO","✓ OK")</f>
+      </c>
+      <c r="I25" s="31">
+        <f>MAX(0,$C$3-SUM($C$7:$F$11))</f>
+      </c>
+    </row>
+    <row r="26" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A26" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="B26" s="29">
+        <f>B11</f>
+      </c>
+      <c r="C26" s="29">
         <f>SUM(C11:F11)</f>
       </c>
-      <c r="H11" s="10">
-        <f>MIN(B11-G11, MAX(0, $C$3-G$12))</f>
-      </c>
-      <c r="I11" s="11">
-        <f>IF(B11=0,0,G11/B11)</f>
-      </c>
-    </row>
-    <row r="12" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="B12" s="15">
-        <f>SUM(B7:B11)</f>
-      </c>
-      <c r="C12" s="15">
-        <f>SUM(C7:C11)</f>
-      </c>
-      <c r="D12" s="15">
-        <f>SUM(D7:D11)</f>
-      </c>
-      <c r="E12" s="15">
-        <f>SUM(E7:E11)</f>
-      </c>
-      <c r="F12" s="15">
-        <f>SUM(F7:F11)</f>
-      </c>
-      <c r="G12" s="15">
-        <f>SUM(G7:G11)</f>
-      </c>
-      <c r="H12" s="15">
-        <f>$C$3-G12</f>
-      </c>
-      <c r="I12" s="16">
-        <f>IF($C$3=0,0,G12/$C$3)</f>
-      </c>
-    </row>
-    <row r="14" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B14" s="4"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="16" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="B16" s="17">
-        <f>$C$3</f>
-      </c>
-      <c r="C16" s="11">
-        <v>1</v>
-      </c>
-      <c r="D16" s="18" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="17" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="19" t="s">
-        <v>9</v>
-      </c>
-      <c r="B17" s="20">
-        <f>G12</f>
-      </c>
-      <c r="C17" s="21">
-        <f>IF($C$3=0,0,B17/$C$3)</f>
-      </c>
-      <c r="D17" s="22">
-        <f>IF(B17&gt;$C$3,"⚠ EXCEDIDO","✓ OK")</f>
-      </c>
-    </row>
-    <row r="18" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="23" t="s">
-        <v>26</v>
-      </c>
-      <c r="B18" s="10">
-        <f>$C$3-B17</f>
-      </c>
-      <c r="C18" s="24">
-        <f>IF($C$3=0,0,B18/$C$3)</f>
-      </c>
-      <c r="D18" s="25">
-        <f>IF(B18&lt;0,"⚠ SIN DISPONIBLE","✓ DISPONIBLE")</f>
-      </c>
-    </row>
-    <row r="20" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A20" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="B20" s="4"/>
-      <c r="C20" s="4"/>
-      <c r="D20" s="4"/>
-      <c r="E20" s="4"/>
-      <c r="F20" s="4"/>
-      <c r="G20" s="4"/>
-      <c r="H20" s="4"/>
-      <c r="I20" s="4"/>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A21" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="E21" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="F21" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="G21" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="H21" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="I21" s="5" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="22" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A22" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B22" s="26">
-        <f>B7</f>
-      </c>
-      <c r="C22" s="26">
-        <f>G7</f>
-      </c>
-      <c r="D22" s="10">
-        <f>H7</f>
-      </c>
-      <c r="E22" s="27">
-        <f>IF(B22=0,0,C22/B22)</f>
-      </c>
-      <c r="F22" s="27">
-        <f>IF($C$3=0,0,C22/$C$3)</f>
-      </c>
-      <c r="G22" s="18">
-        <f>IF(C22&gt;B22,"⚠ EXCEDIDO",IF(C22/B22&gt;0.8,"⚡ ALTO","✓ OK"))</f>
-      </c>
-      <c r="H22" s="18">
-        <f>IF(G12&gt;$C$3,"⚠ EXCEDIDO","✓ OK")</f>
-      </c>
-      <c r="I22" s="26">
-        <f>MAX(0,$C$3-G12)</f>
-      </c>
-    </row>
-    <row r="23" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A23" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="B23" s="28">
-        <f>B8</f>
-      </c>
-      <c r="C23" s="28">
-        <f>G8</f>
-      </c>
-      <c r="D23" s="10">
-        <f>H8</f>
-      </c>
-      <c r="E23" s="29">
-        <f>IF(B23=0,0,C23/B23)</f>
-      </c>
-      <c r="F23" s="29">
-        <f>IF($C$3=0,0,C23/$C$3)</f>
-      </c>
-      <c r="G23" s="30">
-        <f>IF(C23&gt;B23,"⚠ EXCEDIDO",IF(C23/B23&gt;0.8,"⚡ ALTO","✓ OK"))</f>
-      </c>
-      <c r="H23" s="30">
-        <f>IF(G12&gt;$C$3,"⚠ EXCEDIDO","✓ OK")</f>
-      </c>
-      <c r="I23" s="28">
-        <f>MAX(0,$C$3-G12)</f>
-      </c>
-    </row>
-    <row r="24" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A24" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B24" s="26">
-        <f>B9</f>
-      </c>
-      <c r="C24" s="26">
-        <f>G9</f>
-      </c>
-      <c r="D24" s="10">
-        <f>H9</f>
-      </c>
-      <c r="E24" s="27">
-        <f>IF(B24=0,0,C24/B24)</f>
-      </c>
-      <c r="F24" s="27">
-        <f>IF($C$3=0,0,C24/$C$3)</f>
-      </c>
-      <c r="G24" s="18">
-        <f>IF(C24&gt;B24,"⚠ EXCEDIDO",IF(C24/B24&gt;0.8,"⚡ ALTO","✓ OK"))</f>
-      </c>
-      <c r="H24" s="18">
-        <f>IF(G12&gt;$C$3,"⚠ EXCEDIDO","✓ OK")</f>
-      </c>
-      <c r="I24" s="26">
-        <f>MAX(0,$C$3-G12)</f>
-      </c>
-    </row>
-    <row r="25" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A25" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="B25" s="28">
-        <f>B10</f>
-      </c>
-      <c r="C25" s="28">
-        <f>G10</f>
-      </c>
-      <c r="D25" s="10">
-        <f>H10</f>
-      </c>
-      <c r="E25" s="29">
-        <f>IF(B25=0,0,C25/B25)</f>
-      </c>
-      <c r="F25" s="29">
-        <f>IF($C$3=0,0,C25/$C$3)</f>
-      </c>
-      <c r="G25" s="30">
-        <f>IF(C25&gt;B25,"⚠ EXCEDIDO",IF(C25/B25&gt;0.8,"⚡ ALTO","✓ OK"))</f>
-      </c>
-      <c r="H25" s="30">
-        <f>IF(G12&gt;$C$3,"⚠ EXCEDIDO","✓ OK")</f>
-      </c>
-      <c r="I25" s="28">
-        <f>MAX(0,$C$3-G12)</f>
-      </c>
-    </row>
-    <row r="26" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A26" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="B26" s="26">
-        <f>B11</f>
-      </c>
-      <c r="C26" s="26">
-        <f>G11</f>
-      </c>
-      <c r="D26" s="10">
-        <f>H11</f>
-      </c>
-      <c r="E26" s="27">
+      <c r="D26" s="13">
+        <f>MAX(0,H11)</f>
+      </c>
+      <c r="E26" s="30">
         <f>IF(B26=0,0,C26/B26)</f>
       </c>
-      <c r="F26" s="27">
+      <c r="F26" s="30">
         <f>IF($C$3=0,0,C26/$C$3)</f>
       </c>
-      <c r="G26" s="18">
-        <f>IF(C26&gt;B26,"⚠ EXCEDIDO",IF(C26/B26&gt;0.8,"⚡ ALTO","✓ OK"))</f>
-      </c>
-      <c r="H26" s="18">
-        <f>IF(G12&gt;$C$3,"⚠ EXCEDIDO","✓ OK")</f>
-      </c>
-      <c r="I26" s="26">
-        <f>MAX(0,$C$3-G12)</f>
-      </c>
+      <c r="G26" s="21">
+        <f>IF(C26&gt;B26,"⚠ EXCEDIDO",IF(B26=0,"—",IF(C26/B26&gt;0.8,"⚡ ALTO","✓ OK")))</f>
+      </c>
+      <c r="H26" s="21">
+        <f>IF(SUM($C$7:$F$11)&gt;$C$3,"⚠ EXCEDIDO","✓ OK")</f>
+      </c>
+      <c r="I26" s="29">
+        <f>MAX(0,$C$3-SUM($C$7:$F$11))</f>
+      </c>
+    </row>
+    <row r="28" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B28" s="7"/>
+      <c r="C28" s="7"/>
+      <c r="D28" s="7"/>
+      <c r="E28" s="7"/>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" s="22" t="s">
+        <v>38</v>
+      </c>
+      <c r="B29" s="34" t="s">
+        <v>39</v>
+      </c>
+      <c r="C29" s="34"/>
+      <c r="D29" s="34"/>
+      <c r="E29" s="34"/>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="B30" s="34" t="s">
+        <v>41</v>
+      </c>
+      <c r="C30" s="34"/>
+      <c r="D30" s="34"/>
+      <c r="E30" s="34"/>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" s="22" t="s">
+        <v>42</v>
+      </c>
+      <c r="B31" s="34" t="s">
+        <v>43</v>
+      </c>
+      <c r="C31" s="34"/>
+      <c r="D31" s="34"/>
+      <c r="E31" s="34"/>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" s="22" t="s">
+        <v>44</v>
+      </c>
+      <c r="B32" s="34" t="s">
+        <v>45</v>
+      </c>
+      <c r="C32" s="34"/>
+      <c r="D32" s="34"/>
+      <c r="E32" s="34"/>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="B33" s="34" t="s">
+        <v>47</v>
+      </c>
+      <c r="C33" s="34"/>
+      <c r="D33" s="34"/>
+      <c r="E33" s="34"/>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="22" t="s">
+        <v>48</v>
+      </c>
+      <c r="B34" s="34" t="s">
+        <v>49</v>
+      </c>
+      <c r="C34" s="34"/>
+      <c r="D34" s="34"/>
+      <c r="E34" s="34"/>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="16">
     <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="G2:I2"/>
     <mergeCell ref="A3:B3"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="G3:H3"/>
     <mergeCell ref="A5:I5"/>
     <mergeCell ref="A14:E14"/>
     <mergeCell ref="A20:I20"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="B29:E29"/>
+    <mergeCell ref="B30:E30"/>
+    <mergeCell ref="B31:E31"/>
+    <mergeCell ref="B32:E32"/>
+    <mergeCell ref="B33:E33"/>
+    <mergeCell ref="B34:E34"/>
   </mergeCells>
-  <conditionalFormatting sqref="H7:H11">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThan">
-      <formula>0</formula>
+  <conditionalFormatting sqref="G7:G12">
+    <cfRule type="containsText" dxfId="0" priority="1">
+      <formula>NOT(ISERROR(SEARCH("ERROR",G7)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H12">
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="lessThan">
+  <conditionalFormatting sqref="H7:H12">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1349,8 +1659,58 @@
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="2">
+  <conditionalFormatting sqref="G3:H3">
+    <cfRule type="cellIs" dxfId="4" priority="5" operator="lessThanOrEqual">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B17">
+    <cfRule type="containsText" dxfId="5" priority="6">
+      <formula>NOT(ISERROR(SEARCH("ERROR",B17)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B18">
+    <cfRule type="cellIs" dxfId="6" priority="7" operator="equal">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D17:D18">
+    <cfRule type="containsText" dxfId="7" priority="8">
+      <formula>NOT(ISERROR(SEARCH("EXCEDIDO",D17)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="8" priority="9">
+      <formula>NOT(ISERROR(SEARCH("SIN DISPONIBLE",D17)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D22:D26">
+    <cfRule type="cellIs" dxfId="9" priority="10" operator="equal">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G22:H26">
+    <cfRule type="containsText" dxfId="10" priority="11">
+      <formula>NOT(ISERROR(SEARCH("EXCEDIDO",G22)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E22:E26">
+    <cfRule type="cellIs" dxfId="11" priority="12" operator="greaterThan">
+      <formula>1</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="12" priority="13" operator="greaterThan">
+      <formula>0.8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="5">
+    <dataValidation type="decimal" operator="greaterThanOrEqual" showErrorMessage="1" errorTitle="Valor no válido" error="El sublímite no puede ser negativo." sqref="B10:B11">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation type="decimal" operator="greaterThanOrEqual" showErrorMessage="1" errorTitle="Valor no válido" error="El sublímite no puede ser negativo." sqref="B7:B11">
+      <formula1>0</formula1>
+    </dataValidation>
     <dataValidation type="decimal" operator="greaterThanOrEqual" showErrorMessage="1" errorTitle="Valor no válido" error="Las disposiciones no pueden ser negativas." sqref="C10:F11">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation type="decimal" operator="greaterThan" showErrorMessage="1" errorTitle="Valor no válido" error="El límite global debe ser mayor que 0." sqref="C3">
       <formula1>0</formula1>
     </dataValidation>
     <dataValidation type="decimal" operator="greaterThanOrEqual" showErrorMessage="1" errorTitle="Valor no válido" error="Las disposiciones no pueden ser negativas." sqref="C7:F11">
@@ -1366,243 +1726,259 @@
   <sheetPr>
     <tabColor rgb="607D8B"/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="60" customWidth="1"/>
+    <col min="1" max="1" width="65" customWidth="1"/>
     <col min="2" max="2" width="40" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="31" t="s">
-        <v>35</v>
+      <c r="A1" s="35" t="s">
+        <v>50</v>
       </c>
       <c r="B1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="B3" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="B4" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="B5" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="B6" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="B7" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="B8" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>23</v>
+        <v>56</v>
       </c>
       <c r="B9" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="B10" t="s">
-        <v>44</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="B11" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="B12" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>23</v>
+        <v>59</v>
       </c>
       <c r="B13" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="B14" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="B15" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="B16" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="B17" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="B18" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>23</v>
+        <v>64</v>
       </c>
       <c r="B19" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="B20" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="B21" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="B22" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="B23" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="B24" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>23</v>
+        <v>69</v>
       </c>
       <c r="B25" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>57</v>
+        <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="B27" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="B28" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="B29" t="s">
-        <v>23</v>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>73</v>
+      </c>
+      <c r="B30" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>74</v>
+      </c>
+      <c r="B31" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
